--- a/AlphaForge_Fineco_Portfolio.xlsx
+++ b/AlphaForge_Fineco_Portfolio.xlsx
@@ -639,11 +639,11 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -756,11 +756,11 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
@@ -873,11 +873,11 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -990,11 +990,11 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
@@ -1107,11 +1107,11 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -1224,11 +1224,11 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1341,11 +1341,11 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">

--- a/AlphaForge_Fineco_Portfolio.xlsx
+++ b/AlphaForge_Fineco_Portfolio.xlsx
@@ -639,11 +639,11 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -756,11 +756,11 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
@@ -873,11 +873,11 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -990,11 +990,11 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
@@ -1107,11 +1107,11 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -1224,11 +1224,11 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1341,11 +1341,11 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">

--- a/AlphaForge_Fineco_Portfolio.xlsx
+++ b/AlphaForge_Fineco_Portfolio.xlsx
@@ -639,11 +639,11 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -756,11 +756,11 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
@@ -873,11 +873,11 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -990,11 +990,11 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
@@ -1107,11 +1107,11 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -1224,11 +1224,11 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1341,11 +1341,11 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">

--- a/AlphaForge_Fineco_Portfolio.xlsx
+++ b/AlphaForge_Fineco_Portfolio.xlsx
@@ -639,11 +639,11 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -756,11 +756,11 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
@@ -873,11 +873,11 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -990,11 +990,11 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
@@ -1107,11 +1107,11 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -1224,11 +1224,11 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1341,11 +1341,11 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">

--- a/AlphaForge_Fineco_Portfolio.xlsx
+++ b/AlphaForge_Fineco_Portfolio.xlsx
@@ -639,11 +639,11 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -756,11 +756,11 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
@@ -873,11 +873,11 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -990,11 +990,11 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
@@ -1107,11 +1107,11 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -1224,11 +1224,11 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1341,11 +1341,11 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">

--- a/AlphaForge_Fineco_Portfolio.xlsx
+++ b/AlphaForge_Fineco_Portfolio.xlsx
@@ -639,11 +639,11 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -756,11 +756,11 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
@@ -873,11 +873,11 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -990,11 +990,11 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
@@ -1107,11 +1107,11 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -1224,11 +1224,11 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1341,11 +1341,11 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">

--- a/AlphaForge_Fineco_Portfolio.xlsx
+++ b/AlphaForge_Fineco_Portfolio.xlsx
@@ -639,11 +639,11 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -756,11 +756,11 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
@@ -873,11 +873,11 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -990,11 +990,11 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
@@ -1107,11 +1107,11 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -1224,11 +1224,11 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1341,11 +1341,11 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">

--- a/AlphaForge_Fineco_Portfolio.xlsx
+++ b/AlphaForge_Fineco_Portfolio.xlsx
@@ -639,11 +639,11 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -756,11 +756,11 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
@@ -873,11 +873,11 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -990,11 +990,11 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
@@ -1107,11 +1107,11 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -1224,11 +1224,11 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1341,11 +1341,11 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">

--- a/AlphaForge_Fineco_Portfolio.xlsx
+++ b/AlphaForge_Fineco_Portfolio.xlsx
@@ -639,11 +639,11 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -756,11 +756,11 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
@@ -873,11 +873,11 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -990,11 +990,11 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
@@ -1107,11 +1107,11 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -1224,11 +1224,11 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1341,11 +1341,11 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">

--- a/AlphaForge_Fineco_Portfolio.xlsx
+++ b/AlphaForge_Fineco_Portfolio.xlsx
@@ -639,11 +639,11 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -756,11 +756,11 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
@@ -873,11 +873,11 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -990,11 +990,11 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
@@ -1107,11 +1107,11 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -1224,11 +1224,11 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1341,11 +1341,11 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">

--- a/AlphaForge_Fineco_Portfolio.xlsx
+++ b/AlphaForge_Fineco_Portfolio.xlsx
@@ -639,11 +639,11 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -756,11 +756,11 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
@@ -873,11 +873,11 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -990,11 +990,11 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
@@ -1107,11 +1107,11 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -1224,11 +1224,11 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1341,11 +1341,11 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">

--- a/AlphaForge_Fineco_Portfolio.xlsx
+++ b/AlphaForge_Fineco_Portfolio.xlsx
@@ -639,11 +639,11 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -756,11 +756,11 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
@@ -873,11 +873,11 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -990,11 +990,11 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
@@ -1107,11 +1107,11 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -1224,11 +1224,11 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1341,11 +1341,11 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">

--- a/AlphaForge_Fineco_Portfolio.xlsx
+++ b/AlphaForge_Fineco_Portfolio.xlsx
@@ -639,11 +639,11 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -756,11 +756,11 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
@@ -873,11 +873,11 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -990,11 +990,11 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
@@ -1107,11 +1107,11 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -1224,11 +1224,11 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1341,11 +1341,11 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">

--- a/AlphaForge_Fineco_Portfolio.xlsx
+++ b/AlphaForge_Fineco_Portfolio.xlsx
@@ -639,11 +639,11 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -663,14 +663,12 @@
       <c r="Y2" t="n">
         <v>0</v>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
+      <c r="Z2" t="n">
+        <v>0</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Punto zero: non valutare ancora il rendimento, verifica solo corretta esecuzione.</t>
+          <t>Movimento contenuto: monitoraggio ordinario.</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -756,11 +754,11 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
@@ -780,14 +778,12 @@
       <c r="Y3" t="n">
         <v>0</v>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
+      <c r="Z3" t="n">
+        <v>0</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Punto zero: non valutare ancora il rendimento, verifica solo corretta esecuzione.</t>
+          <t>Movimento contenuto: monitoraggio ordinario.</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -873,11 +869,11 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -897,14 +893,12 @@
       <c r="Y4" t="n">
         <v>0</v>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
+      <c r="Z4" t="n">
+        <v>0</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>Punto zero: non valutare ancora il rendimento, verifica solo corretta esecuzione.</t>
+          <t>Movimento contenuto: monitoraggio ordinario.</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -990,11 +984,11 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
@@ -1014,14 +1008,12 @@
       <c r="Y5" t="n">
         <v>0</v>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
+      <c r="Z5" t="n">
+        <v>0</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>Punto zero: non valutare ancora il rendimento, verifica solo corretta esecuzione.</t>
+          <t>Movimento contenuto: monitoraggio ordinario.</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -1107,11 +1099,11 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -1131,14 +1123,12 @@
       <c r="Y6" t="n">
         <v>0</v>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
+      <c r="Z6" t="n">
+        <v>0</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>Punto zero: non valutare ancora il rendimento, verifica solo corretta esecuzione.</t>
+          <t>Movimento contenuto: monitoraggio ordinario.</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -1224,11 +1214,11 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1341,11 +1331,11 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -1478,12 +1468,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Punto zero</t>
+          <t>Prima verifica</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -1514,11 +1504,11 @@
         <v>40</v>
       </c>
       <c r="M2" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Portafoglio appena avviato: una tantum corretta e PAC attivi in baseline. Non valutare ancora la performance; controlla quote, NAV e costi. PAC programmato: 300 EUR/mese.</t>
+          <t>Confronta rendimento, pesi e benchmark; porta al consulente solo le anomalie importanti.</t>
         </is>
       </c>
     </row>

--- a/AlphaForge_Fineco_Portfolio.xlsx
+++ b/AlphaForge_Fineco_Portfolio.xlsx
@@ -639,14 +639,14 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="AC2" t="n">
-        <v>20</v>
+        <v>19.76284584980237</v>
       </c>
     </row>
     <row r="3">
@@ -754,14 +754,14 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -792,7 +792,7 @@
         </is>
       </c>
       <c r="AC3" t="n">
-        <v>20</v>
+        <v>19.76284584980237</v>
       </c>
     </row>
     <row r="4">
@@ -869,14 +869,14 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -907,7 +907,7 @@
         </is>
       </c>
       <c r="AC4" t="n">
-        <v>20</v>
+        <v>19.76284584980237</v>
       </c>
     </row>
     <row r="5">
@@ -984,14 +984,14 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -1022,7 +1022,7 @@
         </is>
       </c>
       <c r="AC5" t="n">
-        <v>20</v>
+        <v>19.76284584980237</v>
       </c>
     </row>
     <row r="6">
@@ -1099,14 +1099,14 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -1137,7 +1137,7 @@
         </is>
       </c>
       <c r="AC6" t="n">
-        <v>20</v>
+        <v>19.76284584980237</v>
       </c>
     </row>
     <row r="7">
@@ -1214,23 +1214,23 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1238,14 +1238,12 @@
       <c r="Y7" t="n">
         <v>0</v>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
+      <c r="Z7" t="n">
+        <v>0</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>PAC impostato: attendere prima rata o confermare se gia' addebitata.</t>
+          <t>Movimento contenuto: monitoraggio ordinario.</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -1254,7 +1252,7 @@
         </is>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>0.5928853754940711</v>
       </c>
     </row>
     <row r="8">
@@ -1331,23 +1329,23 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1355,14 +1353,12 @@
       <c r="Y8" t="n">
         <v>0</v>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
+      <c r="Z8" t="n">
+        <v>0</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>PAC impostato: attendere prima rata o confermare se gia' addebitata.</t>
+          <t>Movimento contenuto: monitoraggio ordinario.</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -1371,7 +1367,7 @@
         </is>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>0.5928853754940711</v>
       </c>
     </row>
   </sheetData>
@@ -1468,7 +1464,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1486,10 +1482,10 @@
         <v>300</v>
       </c>
       <c r="G2" t="n">
-        <v>25000</v>
+        <v>25300</v>
       </c>
       <c r="H2" t="n">
-        <v>25000</v>
+        <v>25300</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -1498,10 +1494,10 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>60</v>
+        <v>59.29</v>
       </c>
       <c r="L2" t="n">
-        <v>40</v>
+        <v>40.71</v>
       </c>
       <c r="M2" t="n">
         <v>75</v>

--- a/AlphaForge_Fineco_Portfolio.xlsx
+++ b/AlphaForge_Fineco_Portfolio.xlsx
@@ -639,11 +639,11 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
@@ -754,11 +754,11 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
@@ -869,11 +869,11 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
@@ -984,11 +984,11 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
@@ -1099,11 +1099,11 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
@@ -1214,11 +1214,11 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
@@ -1329,11 +1329,11 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">

--- a/AlphaForge_Fineco_Portfolio.xlsx
+++ b/AlphaForge_Fineco_Portfolio.xlsx
@@ -639,11 +639,11 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
@@ -754,11 +754,11 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
@@ -869,11 +869,11 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
@@ -984,11 +984,11 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
@@ -1099,11 +1099,11 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
@@ -1214,11 +1214,11 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
@@ -1329,11 +1329,11 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">

--- a/AlphaForge_Fineco_Portfolio.xlsx
+++ b/AlphaForge_Fineco_Portfolio.xlsx
@@ -639,11 +639,11 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
@@ -754,11 +754,11 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
@@ -869,11 +869,11 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
@@ -984,11 +984,11 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
@@ -1099,11 +1099,11 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
@@ -1214,11 +1214,11 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
@@ -1329,11 +1329,11 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">

--- a/AlphaForge_Fineco_Portfolio.xlsx
+++ b/AlphaForge_Fineco_Portfolio.xlsx
@@ -639,11 +639,11 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
@@ -754,11 +754,11 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
@@ -869,11 +869,11 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
@@ -984,11 +984,11 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
@@ -1099,11 +1099,11 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
@@ -1214,11 +1214,11 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
@@ -1329,11 +1329,11 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">

--- a/AlphaForge_Fineco_Portfolio.xlsx
+++ b/AlphaForge_Fineco_Portfolio.xlsx
@@ -639,11 +639,11 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
@@ -754,11 +754,11 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
@@ -869,11 +869,11 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
@@ -984,11 +984,11 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
@@ -1099,11 +1099,11 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
@@ -1214,11 +1214,11 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
@@ -1329,11 +1329,11 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">

--- a/AlphaForge_Fineco_Portfolio.xlsx
+++ b/AlphaForge_Fineco_Portfolio.xlsx
@@ -639,11 +639,11 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
@@ -754,11 +754,11 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
@@ -869,11 +869,11 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
@@ -984,11 +984,11 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
@@ -1099,11 +1099,11 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
@@ -1214,11 +1214,11 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
@@ -1329,11 +1329,11 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">

--- a/AlphaForge_Fineco_Portfolio.xlsx
+++ b/AlphaForge_Fineco_Portfolio.xlsx
@@ -639,11 +639,11 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
@@ -754,11 +754,11 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
@@ -869,11 +869,11 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
@@ -984,11 +984,11 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
@@ -1099,11 +1099,11 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
@@ -1214,11 +1214,11 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
@@ -1329,11 +1329,11 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">

--- a/AlphaForge_Fineco_Portfolio.xlsx
+++ b/AlphaForge_Fineco_Portfolio.xlsx
@@ -639,11 +639,11 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
@@ -754,11 +754,11 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
@@ -869,11 +869,11 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
@@ -984,11 +984,11 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
@@ -1099,11 +1099,11 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
@@ -1214,11 +1214,11 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
@@ -1329,11 +1329,11 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">

--- a/AlphaForge_Fineco_Portfolio.xlsx
+++ b/AlphaForge_Fineco_Portfolio.xlsx
@@ -639,11 +639,11 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
@@ -754,11 +754,11 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
@@ -869,11 +869,11 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
@@ -984,11 +984,11 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
@@ -1099,11 +1099,11 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
@@ -1214,11 +1214,11 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
@@ -1329,11 +1329,11 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">

--- a/AlphaForge_Fineco_Portfolio.xlsx
+++ b/AlphaForge_Fineco_Portfolio.xlsx
@@ -639,11 +639,11 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
@@ -754,11 +754,11 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
@@ -869,11 +869,11 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
@@ -984,11 +984,11 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
@@ -1099,11 +1099,11 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
@@ -1214,11 +1214,11 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
@@ -1329,11 +1329,11 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">

--- a/AlphaForge_Fineco_Portfolio.xlsx
+++ b/AlphaForge_Fineco_Portfolio.xlsx
@@ -639,11 +639,11 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
@@ -754,11 +754,11 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
@@ -869,11 +869,11 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
@@ -984,11 +984,11 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
@@ -1099,11 +1099,11 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
@@ -1214,11 +1214,11 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
@@ -1329,11 +1329,11 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">

--- a/AlphaForge_Fineco_Portfolio.xlsx
+++ b/AlphaForge_Fineco_Portfolio.xlsx
@@ -639,11 +639,11 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
@@ -754,11 +754,11 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
@@ -869,11 +869,11 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
@@ -984,11 +984,11 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
@@ -1099,11 +1099,11 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
@@ -1214,11 +1214,11 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
@@ -1329,11 +1329,11 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">

--- a/AlphaForge_Fineco_Portfolio.xlsx
+++ b/AlphaForge_Fineco_Portfolio.xlsx
@@ -639,11 +639,11 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
@@ -754,11 +754,11 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
@@ -869,11 +869,11 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
@@ -984,11 +984,11 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
@@ -1099,11 +1099,11 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
@@ -1214,11 +1214,11 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
@@ -1329,11 +1329,11 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">

--- a/AlphaForge_Fineco_Portfolio.xlsx
+++ b/AlphaForge_Fineco_Portfolio.xlsx
@@ -639,11 +639,11 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
@@ -754,11 +754,11 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
@@ -869,11 +869,11 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
@@ -984,11 +984,11 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
@@ -1099,11 +1099,11 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
@@ -1214,11 +1214,11 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
@@ -1329,11 +1329,11 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">

--- a/AlphaForge_Fineco_Portfolio.xlsx
+++ b/AlphaForge_Fineco_Portfolio.xlsx
@@ -639,11 +639,11 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
@@ -754,11 +754,11 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
@@ -869,11 +869,11 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
@@ -984,11 +984,11 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
@@ -1099,11 +1099,11 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
@@ -1214,11 +1214,11 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
@@ -1329,11 +1329,11 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">

--- a/AlphaForge_Fineco_Portfolio.xlsx
+++ b/AlphaForge_Fineco_Portfolio.xlsx
@@ -639,11 +639,11 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
@@ -754,11 +754,11 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
@@ -869,11 +869,11 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
@@ -984,11 +984,11 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
@@ -1099,11 +1099,11 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
@@ -1214,11 +1214,11 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
@@ -1329,11 +1329,11 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">

--- a/AlphaForge_Fineco_Portfolio.xlsx
+++ b/AlphaForge_Fineco_Portfolio.xlsx
@@ -639,11 +639,11 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
@@ -754,11 +754,11 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
@@ -869,11 +869,11 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
@@ -984,11 +984,11 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
@@ -1099,11 +1099,11 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
@@ -1214,11 +1214,11 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
@@ -1329,11 +1329,11 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">

--- a/AlphaForge_Fineco_Portfolio.xlsx
+++ b/AlphaForge_Fineco_Portfolio.xlsx
@@ -639,11 +639,11 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
@@ -754,11 +754,11 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
@@ -869,11 +869,11 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
@@ -984,11 +984,11 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
@@ -1099,11 +1099,11 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
@@ -1214,11 +1214,11 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
@@ -1329,11 +1329,11 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">

--- a/AlphaForge_Fineco_Portfolio.xlsx
+++ b/AlphaForge_Fineco_Portfolio.xlsx
@@ -639,11 +639,11 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
@@ -754,11 +754,11 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
@@ -869,11 +869,11 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
@@ -984,11 +984,11 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
@@ -1099,11 +1099,11 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
@@ -1214,11 +1214,11 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
@@ -1329,11 +1329,11 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">

--- a/AlphaForge_Fineco_Portfolio.xlsx
+++ b/AlphaForge_Fineco_Portfolio.xlsx
@@ -639,11 +639,11 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
@@ -754,11 +754,11 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
@@ -869,11 +869,11 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
@@ -984,11 +984,11 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
@@ -1099,11 +1099,11 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
@@ -1214,11 +1214,11 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
@@ -1329,11 +1329,11 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">

--- a/AlphaForge_Fineco_Portfolio.xlsx
+++ b/AlphaForge_Fineco_Portfolio.xlsx
@@ -639,11 +639,11 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
@@ -754,11 +754,11 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
@@ -869,11 +869,11 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
@@ -984,11 +984,11 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
@@ -1099,11 +1099,11 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
@@ -1214,11 +1214,11 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
@@ -1329,11 +1329,11 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">

--- a/AlphaForge_Fineco_Portfolio.xlsx
+++ b/AlphaForge_Fineco_Portfolio.xlsx
@@ -639,11 +639,11 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
@@ -754,11 +754,11 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
@@ -869,11 +869,11 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
@@ -984,11 +984,11 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
@@ -1099,11 +1099,11 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
@@ -1214,11 +1214,11 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
@@ -1329,11 +1329,11 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">

--- a/AlphaForge_Fineco_Portfolio.xlsx
+++ b/AlphaForge_Fineco_Portfolio.xlsx
@@ -639,11 +639,11 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
@@ -754,11 +754,11 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
@@ -869,11 +869,11 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
@@ -984,11 +984,11 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
@@ -1099,11 +1099,11 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
@@ -1214,11 +1214,11 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
@@ -1329,11 +1329,11 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">

--- a/AlphaForge_Fineco_Portfolio.xlsx
+++ b/AlphaForge_Fineco_Portfolio.xlsx
@@ -639,11 +639,11 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
@@ -754,11 +754,11 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
@@ -869,11 +869,11 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
@@ -984,11 +984,11 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
@@ -1099,11 +1099,11 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
@@ -1214,11 +1214,11 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
@@ -1329,11 +1329,11 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">

--- a/AlphaForge_Fineco_Portfolio.xlsx
+++ b/AlphaForge_Fineco_Portfolio.xlsx
@@ -639,11 +639,11 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
@@ -754,11 +754,11 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
@@ -869,11 +869,11 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
@@ -984,11 +984,11 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
@@ -1099,11 +1099,11 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
@@ -1214,11 +1214,11 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
@@ -1329,11 +1329,11 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">

--- a/AlphaForge_Fineco_Portfolio.xlsx
+++ b/AlphaForge_Fineco_Portfolio.xlsx
@@ -639,14 +639,14 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="T2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="AC2" t="n">
-        <v>19.76284584980237</v>
+        <v>19.53125</v>
       </c>
     </row>
     <row r="3">
@@ -754,14 +754,14 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="T3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -792,7 +792,7 @@
         </is>
       </c>
       <c r="AC3" t="n">
-        <v>19.76284584980237</v>
+        <v>19.53125</v>
       </c>
     </row>
     <row r="4">
@@ -869,14 +869,14 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="T4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -907,7 +907,7 @@
         </is>
       </c>
       <c r="AC4" t="n">
-        <v>19.76284584980237</v>
+        <v>19.53125</v>
       </c>
     </row>
     <row r="5">
@@ -984,14 +984,14 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="T5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -1022,7 +1022,7 @@
         </is>
       </c>
       <c r="AC5" t="n">
-        <v>19.76284584980237</v>
+        <v>19.53125</v>
       </c>
     </row>
     <row r="6">
@@ -1099,14 +1099,14 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="T6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -1137,7 +1137,7 @@
         </is>
       </c>
       <c r="AC6" t="n">
-        <v>19.76284584980237</v>
+        <v>19.53125</v>
       </c>
     </row>
     <row r="7">
@@ -1214,23 +1214,23 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="T7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U7" t="n">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="V7" t="n">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="W7" t="n">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1252,7 +1252,7 @@
         </is>
       </c>
       <c r="AC7" t="n">
-        <v>0.5928853754940711</v>
+        <v>1.171875</v>
       </c>
     </row>
     <row r="8">
@@ -1329,23 +1329,23 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="T8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U8" t="n">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="V8" t="n">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="W8" t="n">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1367,7 +1367,7 @@
         </is>
       </c>
       <c r="AC8" t="n">
-        <v>0.5928853754940711</v>
+        <v>1.171875</v>
       </c>
     </row>
   </sheetData>
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1482,10 +1482,10 @@
         <v>300</v>
       </c>
       <c r="G2" t="n">
-        <v>25300</v>
+        <v>25600</v>
       </c>
       <c r="H2" t="n">
-        <v>25300</v>
+        <v>25600</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -1494,10 +1494,10 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>59.29</v>
+        <v>58.59</v>
       </c>
       <c r="L2" t="n">
-        <v>40.71</v>
+        <v>41.41</v>
       </c>
       <c r="M2" t="n">
         <v>75</v>
